--- a/studentlist.xlsx
+++ b/studentlist.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarka\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Campus_technology\backend-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231E9D04-813E-4E37-8E3E-B2BAD9EC7D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DA5526-D3F7-4416-9DAE-E264709349A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="434">
   <si>
     <t>_id</t>
   </si>
@@ -128,9 +128,6 @@
   </si>
   <si>
     <t>2026-27</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>A</t>
@@ -1708,13 +1705,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB48"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="7" max="7" width="19.25" customWidth="1"/>
     <col min="8" max="8" width="30.8125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1800,7 +1797,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1828,17 +1825,17 @@
       <c r="I2" t="s">
         <v>35</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
         <v>36</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>37</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>38</v>
-      </c>
-      <c r="M2" t="s">
-        <v>39</v>
       </c>
       <c r="N2">
         <v>6050</v>
@@ -1853,18 +1850,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
         <v>43</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>44</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>45</v>
-      </c>
-      <c r="D3" t="s">
-        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>32</v>
@@ -1873,25 +1870,25 @@
         <v>33</v>
       </c>
       <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
         <v>47</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
         <v>48</v>
       </c>
-      <c r="J3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>49</v>
-      </c>
-      <c r="M3" t="s">
-        <v>50</v>
       </c>
       <c r="N3">
         <v>6050</v>
@@ -1903,42 +1900,42 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S3" t="s">
+        <v>50</v>
+      </c>
+      <c r="W3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" t="s">
         <v>51</v>
       </c>
-      <c r="W3" t="s">
-        <v>42</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>52</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>53</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>54</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>55</v>
       </c>
-      <c r="AB3" t="s">
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>57</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>58</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>59</v>
-      </c>
-      <c r="D4" t="s">
-        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>32</v>
@@ -1947,22 +1944,22 @@
         <v>33</v>
       </c>
       <c r="G4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s">
         <v>61</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" t="s">
-        <v>62</v>
       </c>
       <c r="N4">
         <v>6050</v>
@@ -1974,33 +1971,33 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB4" t="s">
         <v>63</v>
       </c>
-      <c r="AB4" t="s">
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>65</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>66</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
@@ -2009,22 +2006,22 @@
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
         <v>36</v>
       </c>
-      <c r="K5" t="s">
-        <v>37</v>
-      </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N5">
         <v>6050</v>
@@ -2036,33 +2033,33 @@
         <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB5" t="s">
         <v>70</v>
       </c>
-      <c r="AB5" t="s">
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A6" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>73</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
@@ -2071,22 +2068,22 @@
         <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
         <v>36</v>
       </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
       <c r="L6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N6">
         <v>6050</v>
@@ -2098,33 +2095,33 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB6" t="s">
         <v>77</v>
       </c>
-      <c r="AB6" t="s">
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="7" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>79</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>80</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>81</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
@@ -2133,25 +2130,25 @@
         <v>33</v>
       </c>
       <c r="G7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" t="s">
         <v>83</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" t="s">
-        <v>62</v>
-      </c>
-      <c r="M7" t="s">
-        <v>84</v>
       </c>
       <c r="N7">
         <v>6050</v>
@@ -2163,42 +2160,42 @@
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S7" t="s">
+        <v>84</v>
+      </c>
+      <c r="W7" t="s">
+        <v>41</v>
+      </c>
+      <c r="X7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y7" t="s">
         <v>85</v>
       </c>
-      <c r="W7" t="s">
-        <v>42</v>
-      </c>
-      <c r="X7" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>86</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>87</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>88</v>
       </c>
-      <c r="AB7" t="s">
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A8" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>90</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>91</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>92</v>
-      </c>
-      <c r="D8" t="s">
-        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -2207,22 +2204,22 @@
         <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8" t="s">
         <v>36</v>
       </c>
-      <c r="K8" t="s">
-        <v>37</v>
-      </c>
       <c r="L8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N8">
         <v>6050</v>
@@ -2234,33 +2231,33 @@
         <v>0</v>
       </c>
       <c r="R8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA8" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB8" t="s">
         <v>95</v>
       </c>
-      <c r="AB8" t="s">
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>97</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>98</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>99</v>
-      </c>
-      <c r="D9" t="s">
-        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>32</v>
@@ -2269,22 +2266,22 @@
         <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
         <v>36</v>
       </c>
-      <c r="K9" t="s">
-        <v>37</v>
-      </c>
       <c r="L9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N9">
         <v>6050</v>
@@ -2296,36 +2293,36 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S9" t="s">
+        <v>101</v>
+      </c>
+      <c r="W9" t="s">
+        <v>41</v>
+      </c>
+      <c r="X9" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA9" t="s">
         <v>102</v>
       </c>
-      <c r="W9" t="s">
-        <v>42</v>
-      </c>
-      <c r="X9" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>103</v>
       </c>
-      <c r="AB9" t="s">
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A10" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>105</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>106</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>107</v>
-      </c>
-      <c r="D10" t="s">
-        <v>108</v>
       </c>
       <c r="E10" t="s">
         <v>32</v>
@@ -2334,25 +2331,25 @@
         <v>33</v>
       </c>
       <c r="G10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" t="s">
         <v>109</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" t="s">
-        <v>36</v>
-      </c>
-      <c r="K10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" t="s">
-        <v>62</v>
-      </c>
-      <c r="M10" t="s">
-        <v>110</v>
       </c>
       <c r="N10">
         <v>6050</v>
@@ -2364,42 +2361,42 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
+        <v>40</v>
+      </c>
+      <c r="S10" t="s">
+        <v>50</v>
+      </c>
+      <c r="W10" t="s">
         <v>41</v>
       </c>
-      <c r="S10" t="s">
+      <c r="X10" t="s">
         <v>51</v>
       </c>
-      <c r="W10" t="s">
-        <v>42</v>
-      </c>
-      <c r="X10" t="s">
-        <v>52</v>
-      </c>
       <c r="Y10" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z10" t="s">
         <v>111</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="AA10" t="s">
         <v>112</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AB10" t="s">
         <v>113</v>
       </c>
-      <c r="AB10" t="s">
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A11" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>115</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>116</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>117</v>
-      </c>
-      <c r="D11" t="s">
-        <v>118</v>
       </c>
       <c r="E11" t="s">
         <v>32</v>
@@ -2408,25 +2405,25 @@
         <v>33</v>
       </c>
       <c r="G11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
         <v>119</v>
       </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" t="s">
         <v>120</v>
-      </c>
-      <c r="J11" t="s">
-        <v>36</v>
-      </c>
-      <c r="K11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L11" t="s">
-        <v>62</v>
-      </c>
-      <c r="M11" t="s">
-        <v>121</v>
       </c>
       <c r="N11">
         <v>6050</v>
@@ -2438,42 +2435,42 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S11" t="s">
+        <v>121</v>
+      </c>
+      <c r="W11" t="s">
+        <v>41</v>
+      </c>
+      <c r="X11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y11" t="s">
         <v>122</v>
       </c>
-      <c r="W11" t="s">
-        <v>42</v>
-      </c>
-      <c r="X11" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y11" t="s">
+      <c r="Z11" t="s">
         <v>123</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AA11" t="s">
         <v>124</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AB11" t="s">
         <v>125</v>
       </c>
-      <c r="AB11" t="s">
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A12" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="12" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>127</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>128</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>129</v>
-      </c>
-      <c r="D12" t="s">
-        <v>130</v>
       </c>
       <c r="E12" t="s">
         <v>32</v>
@@ -2482,25 +2479,25 @@
         <v>33</v>
       </c>
       <c r="G12" t="s">
+        <v>130</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" t="s">
         <v>131</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>120</v>
-      </c>
-      <c r="J12" t="s">
-        <v>36</v>
-      </c>
-      <c r="K12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M12" t="s">
-        <v>132</v>
       </c>
       <c r="N12">
         <v>6050</v>
@@ -2512,42 +2509,42 @@
         <v>0</v>
       </c>
       <c r="R12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y12" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z12" t="s">
         <v>133</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AA12" t="s">
         <v>134</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>135</v>
       </c>
-      <c r="AB12" t="s">
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A13" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>137</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>138</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>139</v>
-      </c>
-      <c r="D13" t="s">
-        <v>140</v>
       </c>
       <c r="E13" t="s">
         <v>32</v>
@@ -2556,25 +2553,25 @@
         <v>33</v>
       </c>
       <c r="G13" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" t="s">
         <v>141</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>120</v>
-      </c>
-      <c r="J13" t="s">
-        <v>36</v>
-      </c>
-      <c r="K13" t="s">
-        <v>37</v>
-      </c>
-      <c r="L13" t="s">
-        <v>62</v>
-      </c>
-      <c r="M13" t="s">
-        <v>142</v>
       </c>
       <c r="N13">
         <v>6050</v>
@@ -2586,42 +2583,42 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y13" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z13" t="s">
         <v>143</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AA13" t="s">
         <v>144</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AB13" t="s">
         <v>145</v>
       </c>
-      <c r="AB13" t="s">
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A14" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>147</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>148</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>149</v>
-      </c>
-      <c r="D14" t="s">
-        <v>150</v>
       </c>
       <c r="E14" t="s">
         <v>32</v>
@@ -2630,22 +2627,22 @@
         <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H14">
         <v>2</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14" t="s">
         <v>36</v>
       </c>
-      <c r="K14" t="s">
-        <v>37</v>
-      </c>
       <c r="L14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N14">
         <v>6050</v>
@@ -2657,33 +2654,33 @@
         <v>0</v>
       </c>
       <c r="R14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA14" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB14" t="s">
         <v>153</v>
       </c>
-      <c r="AB14" t="s">
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A15" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>155</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>156</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>157</v>
-      </c>
-      <c r="D15" t="s">
-        <v>158</v>
       </c>
       <c r="E15" t="s">
         <v>32</v>
@@ -2692,22 +2689,22 @@
         <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H15">
         <v>2</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J15" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15" t="s">
         <v>36</v>
       </c>
-      <c r="K15" t="s">
-        <v>37</v>
-      </c>
       <c r="L15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N15">
         <v>6050</v>
@@ -2719,39 +2716,39 @@
         <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Z15" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA15" t="s">
         <v>160</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>161</v>
       </c>
-      <c r="AB15" t="s">
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A16" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>163</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>164</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>165</v>
-      </c>
-      <c r="D16" t="s">
-        <v>166</v>
       </c>
       <c r="E16" t="s">
         <v>32</v>
@@ -2760,22 +2757,22 @@
         <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H16">
         <v>2</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
-      </c>
-      <c r="J16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16" t="s">
         <v>36</v>
       </c>
-      <c r="K16" t="s">
-        <v>37</v>
-      </c>
       <c r="L16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N16">
         <v>6050</v>
@@ -2787,36 +2784,36 @@
         <v>0</v>
       </c>
       <c r="R16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y16" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA16" t="s">
         <v>168</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB16" t="s">
         <v>169</v>
       </c>
-      <c r="AB16" t="s">
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A17" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="17" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>171</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>172</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>173</v>
-      </c>
-      <c r="D17" t="s">
-        <v>174</v>
       </c>
       <c r="E17" t="s">
         <v>32</v>
@@ -2825,25 +2822,25 @@
         <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H17">
         <v>2</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
-      </c>
-      <c r="J17" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17" t="s">
         <v>36</v>
       </c>
-      <c r="K17" t="s">
-        <v>37</v>
-      </c>
       <c r="L17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N17">
         <v>6050</v>
@@ -2855,42 +2852,42 @@
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y17" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z17" t="s">
         <v>177</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="AA17" t="s">
         <v>178</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB17" t="s">
         <v>179</v>
       </c>
-      <c r="AB17" t="s">
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A18" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>181</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>182</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>183</v>
-      </c>
-      <c r="D18" t="s">
-        <v>184</v>
       </c>
       <c r="E18" t="s">
         <v>32</v>
@@ -2899,25 +2896,25 @@
         <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H18">
         <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
-      </c>
-      <c r="J18" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18" t="s">
         <v>36</v>
       </c>
-      <c r="K18" t="s">
-        <v>37</v>
-      </c>
       <c r="L18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N18">
         <v>6050</v>
@@ -2929,42 +2926,42 @@
         <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S18" t="s">
+        <v>50</v>
+      </c>
+      <c r="W18" t="s">
+        <v>41</v>
+      </c>
+      <c r="X18" t="s">
         <v>51</v>
       </c>
-      <c r="W18" t="s">
-        <v>42</v>
-      </c>
-      <c r="X18" t="s">
-        <v>52</v>
-      </c>
       <c r="Y18" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z18" t="s">
         <v>187</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="AA18" t="s">
         <v>188</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AB18" t="s">
         <v>189</v>
       </c>
-      <c r="AB18" t="s">
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A19" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="19" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>191</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>192</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>193</v>
-      </c>
-      <c r="D19" t="s">
-        <v>194</v>
       </c>
       <c r="E19" t="s">
         <v>32</v>
@@ -2973,22 +2970,22 @@
         <v>33</v>
       </c>
       <c r="G19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H19">
         <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
-      </c>
-      <c r="J19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19" t="s">
         <v>36</v>
       </c>
-      <c r="K19" t="s">
-        <v>37</v>
-      </c>
       <c r="L19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N19">
         <v>6050</v>
@@ -3000,33 +2997,33 @@
         <v>0</v>
       </c>
       <c r="R19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA19" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB19" t="s">
         <v>196</v>
       </c>
-      <c r="AB19" t="s">
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A20" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="20" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>198</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>199</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>200</v>
-      </c>
-      <c r="D20" t="s">
-        <v>201</v>
       </c>
       <c r="E20" t="s">
         <v>32</v>
@@ -3035,25 +3032,25 @@
         <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H20">
         <v>2</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
-      </c>
-      <c r="J20" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20" t="s">
         <v>36</v>
       </c>
-      <c r="K20" t="s">
-        <v>37</v>
-      </c>
       <c r="L20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N20">
         <v>6050</v>
@@ -3065,36 +3062,36 @@
         <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA20" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB20" t="s">
         <v>204</v>
       </c>
-      <c r="AB20" t="s">
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A21" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>206</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>207</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>208</v>
-      </c>
-      <c r="D21" t="s">
-        <v>209</v>
       </c>
       <c r="E21" t="s">
         <v>32</v>
@@ -3103,22 +3100,22 @@
         <v>33</v>
       </c>
       <c r="G21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H21">
         <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>120</v>
-      </c>
-      <c r="J21" t="s">
+        <v>119</v>
+      </c>
+      <c r="J21">
+        <v>3</v>
+      </c>
+      <c r="K21" t="s">
         <v>36</v>
       </c>
-      <c r="K21" t="s">
-        <v>37</v>
-      </c>
       <c r="L21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N21">
         <v>6050</v>
@@ -3130,33 +3127,33 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA21" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB21" t="s">
         <v>211</v>
       </c>
-      <c r="AB21" t="s">
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A22" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="22" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>213</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>214</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>215</v>
-      </c>
-      <c r="D22" t="s">
-        <v>216</v>
       </c>
       <c r="E22" t="s">
         <v>32</v>
@@ -3165,22 +3162,22 @@
         <v>33</v>
       </c>
       <c r="G22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H22">
         <v>2</v>
       </c>
       <c r="I22" t="s">
-        <v>120</v>
-      </c>
-      <c r="J22" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22" t="s">
         <v>36</v>
       </c>
-      <c r="K22" t="s">
-        <v>37</v>
-      </c>
       <c r="L22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N22">
         <v>6050</v>
@@ -3192,33 +3189,33 @@
         <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA22" t="s">
+        <v>217</v>
+      </c>
+      <c r="AB22" t="s">
         <v>218</v>
       </c>
-      <c r="AB22" t="s">
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A23" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="23" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>220</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>221</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>222</v>
-      </c>
-      <c r="D23" t="s">
-        <v>223</v>
       </c>
       <c r="E23" t="s">
         <v>32</v>
@@ -3227,25 +3224,25 @@
         <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H23">
         <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>120</v>
-      </c>
-      <c r="J23" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23" t="s">
         <v>36</v>
       </c>
-      <c r="K23" t="s">
-        <v>37</v>
-      </c>
       <c r="L23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N23">
         <v>6050</v>
@@ -3257,42 +3254,42 @@
         <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S23" t="s">
+        <v>225</v>
+      </c>
+      <c r="W23" t="s">
+        <v>41</v>
+      </c>
+      <c r="X23" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y23" t="s">
         <v>226</v>
       </c>
-      <c r="W23" t="s">
-        <v>42</v>
-      </c>
-      <c r="X23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y23" t="s">
+      <c r="Z23" t="s">
         <v>227</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="AA23" t="s">
         <v>228</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB23" t="s">
         <v>229</v>
       </c>
-      <c r="AB23" t="s">
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A24" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="24" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>231</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>232</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>233</v>
-      </c>
-      <c r="D24" t="s">
-        <v>234</v>
       </c>
       <c r="E24" t="s">
         <v>32</v>
@@ -3301,22 +3298,22 @@
         <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H24">
         <v>3</v>
       </c>
       <c r="I24" t="s">
-        <v>120</v>
-      </c>
-      <c r="J24" t="s">
+        <v>119</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24" t="s">
         <v>36</v>
       </c>
-      <c r="K24" t="s">
-        <v>37</v>
-      </c>
       <c r="L24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N24">
         <v>6050</v>
@@ -3328,33 +3325,33 @@
         <v>0</v>
       </c>
       <c r="R24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA24" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB24" t="s">
         <v>236</v>
       </c>
-      <c r="AB24" t="s">
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A25" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="25" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>238</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>239</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>240</v>
-      </c>
-      <c r="D25" t="s">
-        <v>241</v>
       </c>
       <c r="E25" t="s">
         <v>32</v>
@@ -3363,22 +3360,22 @@
         <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H25">
         <v>3</v>
       </c>
       <c r="I25" t="s">
-        <v>120</v>
-      </c>
-      <c r="J25" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+      <c r="K25" t="s">
         <v>36</v>
       </c>
-      <c r="K25" t="s">
-        <v>37</v>
-      </c>
       <c r="L25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N25">
         <v>6050</v>
@@ -3390,33 +3387,33 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA25" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB25" t="s">
         <v>243</v>
       </c>
-      <c r="AB25" t="s">
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A26" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="26" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>245</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>246</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>247</v>
-      </c>
-      <c r="D26" t="s">
-        <v>248</v>
       </c>
       <c r="E26" t="s">
         <v>32</v>
@@ -3425,22 +3422,22 @@
         <v>33</v>
       </c>
       <c r="G26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H26">
         <v>3</v>
       </c>
       <c r="I26" t="s">
-        <v>120</v>
-      </c>
-      <c r="J26" t="s">
+        <v>119</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26" t="s">
         <v>36</v>
       </c>
-      <c r="K26" t="s">
-        <v>37</v>
-      </c>
       <c r="L26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N26">
         <v>6050</v>
@@ -3452,33 +3449,33 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA26" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB26" t="s">
         <v>250</v>
       </c>
-      <c r="AB26" t="s">
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A27" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="27" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>252</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>253</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>254</v>
-      </c>
-      <c r="D27" t="s">
-        <v>255</v>
       </c>
       <c r="E27" t="s">
         <v>32</v>
@@ -3487,22 +3484,22 @@
         <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H27">
         <v>3</v>
       </c>
       <c r="I27" t="s">
-        <v>120</v>
-      </c>
-      <c r="J27" t="s">
+        <v>119</v>
+      </c>
+      <c r="J27">
+        <v>4</v>
+      </c>
+      <c r="K27" t="s">
         <v>36</v>
       </c>
-      <c r="K27" t="s">
-        <v>37</v>
-      </c>
       <c r="L27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N27">
         <v>6050</v>
@@ -3514,36 +3511,36 @@
         <v>0</v>
       </c>
       <c r="R27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA27" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB27" t="s">
         <v>257</v>
       </c>
-      <c r="AB27" t="s">
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A28" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="28" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>259</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>260</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>261</v>
-      </c>
-      <c r="D28" t="s">
-        <v>262</v>
       </c>
       <c r="E28" t="s">
         <v>32</v>
@@ -3552,25 +3549,25 @@
         <v>33</v>
       </c>
       <c r="G28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H28">
         <v>3</v>
       </c>
       <c r="I28" t="s">
-        <v>120</v>
-      </c>
-      <c r="J28" t="s">
+        <v>119</v>
+      </c>
+      <c r="J28">
+        <v>4</v>
+      </c>
+      <c r="K28" t="s">
         <v>36</v>
       </c>
-      <c r="K28" t="s">
-        <v>37</v>
-      </c>
       <c r="L28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N28">
         <v>6050</v>
@@ -3582,42 +3579,42 @@
         <v>0</v>
       </c>
       <c r="R28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y28" t="s">
+        <v>264</v>
+      </c>
+      <c r="Z28" t="s">
         <v>265</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AA28" t="s">
         <v>266</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AB28" t="s">
         <v>267</v>
       </c>
-      <c r="AB28" t="s">
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A29" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="29" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>269</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>270</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>271</v>
-      </c>
-      <c r="D29" t="s">
-        <v>272</v>
       </c>
       <c r="E29" t="s">
         <v>32</v>
@@ -3626,25 +3623,25 @@
         <v>33</v>
       </c>
       <c r="G29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H29">
         <v>3</v>
       </c>
       <c r="I29" t="s">
-        <v>120</v>
-      </c>
-      <c r="J29" t="s">
+        <v>119</v>
+      </c>
+      <c r="J29">
+        <v>4</v>
+      </c>
+      <c r="K29" t="s">
         <v>36</v>
       </c>
-      <c r="K29" t="s">
-        <v>37</v>
-      </c>
       <c r="L29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N29">
         <v>6050</v>
@@ -3656,33 +3653,33 @@
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA29" t="s">
+        <v>274</v>
+      </c>
+      <c r="AB29" t="s">
         <v>275</v>
       </c>
-      <c r="AB29" t="s">
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A30" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="30" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>277</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>278</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>279</v>
-      </c>
-      <c r="D30" t="s">
-        <v>280</v>
       </c>
       <c r="E30" t="s">
         <v>32</v>
@@ -3691,25 +3688,25 @@
         <v>33</v>
       </c>
       <c r="G30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H30">
         <v>3</v>
       </c>
       <c r="I30" t="s">
-        <v>120</v>
-      </c>
-      <c r="J30" t="s">
+        <v>119</v>
+      </c>
+      <c r="J30">
+        <v>4</v>
+      </c>
+      <c r="K30" t="s">
         <v>36</v>
       </c>
-      <c r="K30" t="s">
-        <v>37</v>
-      </c>
       <c r="L30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N30">
         <v>6050</v>
@@ -3721,42 +3718,42 @@
         <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y30" t="s">
+        <v>282</v>
+      </c>
+      <c r="Z30" t="s">
         <v>283</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AA30" t="s">
         <v>284</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB30" t="s">
         <v>285</v>
       </c>
-      <c r="AB30" t="s">
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A31" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="31" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>287</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>288</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>289</v>
-      </c>
-      <c r="D31" t="s">
-        <v>290</v>
       </c>
       <c r="E31" t="s">
         <v>32</v>
@@ -3765,22 +3762,22 @@
         <v>33</v>
       </c>
       <c r="G31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H31">
         <v>3</v>
       </c>
       <c r="I31" t="s">
-        <v>120</v>
-      </c>
-      <c r="J31" t="s">
+        <v>119</v>
+      </c>
+      <c r="J31">
+        <v>4</v>
+      </c>
+      <c r="K31" t="s">
         <v>36</v>
       </c>
-      <c r="K31" t="s">
-        <v>37</v>
-      </c>
       <c r="L31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N31">
         <v>6050</v>
@@ -3792,36 +3789,36 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA31" t="s">
+        <v>291</v>
+      </c>
+      <c r="AB31" t="s">
         <v>292</v>
       </c>
-      <c r="AB31" t="s">
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A32" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="32" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>294</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>295</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>296</v>
-      </c>
-      <c r="D32" t="s">
-        <v>297</v>
       </c>
       <c r="E32" t="s">
         <v>32</v>
@@ -3830,22 +3827,22 @@
         <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H32">
         <v>3</v>
       </c>
       <c r="I32" t="s">
-        <v>120</v>
-      </c>
-      <c r="J32" t="s">
+        <v>119</v>
+      </c>
+      <c r="J32">
+        <v>4</v>
+      </c>
+      <c r="K32" t="s">
         <v>36</v>
       </c>
-      <c r="K32" t="s">
-        <v>37</v>
-      </c>
       <c r="L32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N32">
         <v>6050</v>
@@ -3857,36 +3854,36 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y32" t="s">
+        <v>298</v>
+      </c>
+      <c r="AA32" t="s">
         <v>299</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AB32" t="s">
         <v>300</v>
       </c>
-      <c r="AB32" t="s">
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A33" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="33" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>302</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>303</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>304</v>
-      </c>
-      <c r="D33" t="s">
-        <v>305</v>
       </c>
       <c r="E33" t="s">
         <v>32</v>
@@ -3895,22 +3892,22 @@
         <v>33</v>
       </c>
       <c r="G33" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H33">
         <v>3</v>
       </c>
       <c r="I33" t="s">
-        <v>120</v>
-      </c>
-      <c r="J33" t="s">
+        <v>119</v>
+      </c>
+      <c r="J33">
+        <v>5</v>
+      </c>
+      <c r="K33" t="s">
         <v>36</v>
       </c>
-      <c r="K33" t="s">
-        <v>37</v>
-      </c>
       <c r="L33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N33">
         <v>6050</v>
@@ -3922,33 +3919,33 @@
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA33" t="s">
+        <v>306</v>
+      </c>
+      <c r="AB33" t="s">
         <v>307</v>
       </c>
-      <c r="AB33" t="s">
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A34" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="34" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>309</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>310</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>311</v>
-      </c>
-      <c r="D34" t="s">
-        <v>312</v>
       </c>
       <c r="E34" t="s">
         <v>32</v>
@@ -3957,22 +3954,22 @@
         <v>33</v>
       </c>
       <c r="G34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H34">
         <v>4</v>
       </c>
       <c r="I34" t="s">
+        <v>313</v>
+      </c>
+      <c r="J34">
+        <v>5</v>
+      </c>
+      <c r="K34" t="s">
+        <v>36</v>
+      </c>
+      <c r="L34" t="s">
         <v>314</v>
-      </c>
-      <c r="J34" t="s">
-        <v>36</v>
-      </c>
-      <c r="K34" t="s">
-        <v>37</v>
-      </c>
-      <c r="L34" t="s">
-        <v>315</v>
       </c>
       <c r="N34">
         <v>6050</v>
@@ -3984,36 +3981,36 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X34" t="s">
+        <v>315</v>
+      </c>
+      <c r="AA34" t="s">
         <v>316</v>
       </c>
-      <c r="AA34" t="s">
+      <c r="AB34" t="s">
         <v>317</v>
       </c>
-      <c r="AB34" t="s">
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A35" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="35" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>319</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>320</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>321</v>
-      </c>
-      <c r="D35" t="s">
-        <v>322</v>
       </c>
       <c r="E35" t="s">
         <v>32</v>
@@ -4022,25 +4019,25 @@
         <v>33</v>
       </c>
       <c r="G35" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H35">
         <v>4</v>
       </c>
       <c r="I35" t="s">
+        <v>323</v>
+      </c>
+      <c r="J35">
+        <v>5</v>
+      </c>
+      <c r="K35" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" t="s">
+        <v>314</v>
+      </c>
+      <c r="M35" t="s">
         <v>324</v>
-      </c>
-      <c r="J35" t="s">
-        <v>36</v>
-      </c>
-      <c r="K35" t="s">
-        <v>37</v>
-      </c>
-      <c r="L35" t="s">
-        <v>315</v>
-      </c>
-      <c r="M35" t="s">
-        <v>325</v>
       </c>
       <c r="N35">
         <v>6050</v>
@@ -4052,39 +4049,39 @@
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S35" t="s">
+        <v>50</v>
+      </c>
+      <c r="W35" t="s">
+        <v>41</v>
+      </c>
+      <c r="X35" t="s">
         <v>51</v>
       </c>
-      <c r="W35" t="s">
-        <v>42</v>
-      </c>
-      <c r="X35" t="s">
-        <v>52</v>
-      </c>
       <c r="Y35" t="s">
+        <v>325</v>
+      </c>
+      <c r="AA35" t="s">
         <v>326</v>
       </c>
-      <c r="AA35" t="s">
+      <c r="AB35" t="s">
         <v>327</v>
       </c>
-      <c r="AB35" t="s">
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A36" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="36" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>329</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>330</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>331</v>
-      </c>
-      <c r="D36" t="s">
-        <v>332</v>
       </c>
       <c r="E36" t="s">
         <v>32</v>
@@ -4093,25 +4090,25 @@
         <v>33</v>
       </c>
       <c r="G36" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H36">
         <v>4</v>
       </c>
       <c r="I36" t="s">
-        <v>324</v>
-      </c>
-      <c r="J36" t="s">
+        <v>323</v>
+      </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
+      <c r="K36" t="s">
         <v>36</v>
       </c>
-      <c r="K36" t="s">
-        <v>37</v>
-      </c>
       <c r="L36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N36">
         <v>6050</v>
@@ -4123,42 +4120,42 @@
         <v>0</v>
       </c>
       <c r="R36" t="s">
+        <v>40</v>
+      </c>
+      <c r="S36" t="s">
+        <v>84</v>
+      </c>
+      <c r="W36" t="s">
         <v>41</v>
       </c>
-      <c r="S36" t="s">
-        <v>85</v>
-      </c>
-      <c r="W36" t="s">
-        <v>42</v>
-      </c>
       <c r="X36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y36" t="s">
+        <v>334</v>
+      </c>
+      <c r="Z36" t="s">
         <v>335</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="AA36" t="s">
         <v>336</v>
       </c>
-      <c r="AA36" t="s">
+      <c r="AB36" t="s">
         <v>337</v>
       </c>
-      <c r="AB36" t="s">
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A37" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="37" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>339</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>340</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>341</v>
-      </c>
-      <c r="D37" t="s">
-        <v>342</v>
       </c>
       <c r="E37" t="s">
         <v>32</v>
@@ -4167,22 +4164,22 @@
         <v>33</v>
       </c>
       <c r="G37" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H37">
         <v>4</v>
       </c>
       <c r="I37" t="s">
-        <v>324</v>
-      </c>
-      <c r="J37" t="s">
+        <v>323</v>
+      </c>
+      <c r="J37">
+        <v>5</v>
+      </c>
+      <c r="K37" t="s">
         <v>36</v>
       </c>
-      <c r="K37" t="s">
-        <v>37</v>
-      </c>
       <c r="L37" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N37">
         <v>6050</v>
@@ -4194,42 +4191,42 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y37" t="s">
+        <v>343</v>
+      </c>
+      <c r="Z37" t="s">
         <v>344</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="AA37" t="s">
         <v>345</v>
       </c>
-      <c r="AA37" t="s">
+      <c r="AB37" t="s">
         <v>346</v>
       </c>
-      <c r="AB37" t="s">
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A38" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="38" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>348</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>349</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>350</v>
-      </c>
-      <c r="D38" t="s">
-        <v>351</v>
       </c>
       <c r="E38" t="s">
         <v>32</v>
@@ -4238,25 +4235,25 @@
         <v>33</v>
       </c>
       <c r="G38" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H38">
         <v>4</v>
       </c>
       <c r="I38" t="s">
-        <v>324</v>
-      </c>
-      <c r="J38" t="s">
+        <v>323</v>
+      </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38" t="s">
         <v>36</v>
       </c>
-      <c r="K38" t="s">
-        <v>37</v>
-      </c>
       <c r="L38" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N38">
         <v>6050</v>
@@ -4268,42 +4265,42 @@
         <v>0</v>
       </c>
       <c r="R38" t="s">
+        <v>40</v>
+      </c>
+      <c r="S38" t="s">
+        <v>84</v>
+      </c>
+      <c r="W38" t="s">
         <v>41</v>
       </c>
-      <c r="S38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W38" t="s">
-        <v>42</v>
-      </c>
       <c r="X38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y38" t="s">
+        <v>353</v>
+      </c>
+      <c r="Z38" t="s">
         <v>354</v>
       </c>
-      <c r="Z38" t="s">
+      <c r="AA38" t="s">
         <v>355</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AB38" t="s">
         <v>356</v>
       </c>
-      <c r="AB38" t="s">
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A39" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="39" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>358</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>359</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>360</v>
-      </c>
-      <c r="D39" t="s">
-        <v>361</v>
       </c>
       <c r="E39" t="s">
         <v>32</v>
@@ -4312,25 +4309,25 @@
         <v>33</v>
       </c>
       <c r="G39" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H39">
         <v>4</v>
       </c>
       <c r="I39" t="s">
-        <v>324</v>
-      </c>
-      <c r="J39" t="s">
+        <v>323</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
+      <c r="K39" t="s">
         <v>36</v>
       </c>
-      <c r="K39" t="s">
-        <v>37</v>
-      </c>
       <c r="L39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="N39">
         <v>6050</v>
@@ -4342,42 +4339,42 @@
         <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y39" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z39" t="s">
         <v>364</v>
       </c>
-      <c r="Z39" t="s">
+      <c r="AA39" t="s">
         <v>365</v>
       </c>
-      <c r="AA39" t="s">
+      <c r="AB39" t="s">
         <v>366</v>
       </c>
-      <c r="AB39" t="s">
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A40" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="40" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>368</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>369</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>370</v>
-      </c>
-      <c r="D40" t="s">
-        <v>371</v>
       </c>
       <c r="E40" t="s">
         <v>32</v>
@@ -4386,25 +4383,25 @@
         <v>33</v>
       </c>
       <c r="G40" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H40">
         <v>6</v>
       </c>
       <c r="I40" t="s">
-        <v>324</v>
-      </c>
-      <c r="J40" t="s">
+        <v>323</v>
+      </c>
+      <c r="J40">
+        <v>5</v>
+      </c>
+      <c r="K40" t="s">
         <v>36</v>
       </c>
-      <c r="K40" t="s">
-        <v>37</v>
-      </c>
       <c r="L40" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M40" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="N40">
         <v>6050</v>
@@ -4416,42 +4413,42 @@
         <v>0</v>
       </c>
       <c r="R40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S40" t="s">
+        <v>50</v>
+      </c>
+      <c r="W40" t="s">
+        <v>41</v>
+      </c>
+      <c r="X40" t="s">
         <v>51</v>
       </c>
-      <c r="W40" t="s">
-        <v>42</v>
-      </c>
-      <c r="X40" t="s">
-        <v>52</v>
-      </c>
       <c r="Y40" t="s">
+        <v>373</v>
+      </c>
+      <c r="Z40" t="s">
         <v>374</v>
       </c>
-      <c r="Z40" t="s">
+      <c r="AA40" t="s">
         <v>375</v>
       </c>
-      <c r="AA40" t="s">
+      <c r="AB40" t="s">
         <v>376</v>
       </c>
-      <c r="AB40" t="s">
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A41" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="41" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>378</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>379</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>380</v>
-      </c>
-      <c r="D41" t="s">
-        <v>381</v>
       </c>
       <c r="E41" t="s">
         <v>32</v>
@@ -4460,22 +4457,22 @@
         <v>33</v>
       </c>
       <c r="G41" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H41">
         <v>6</v>
       </c>
       <c r="I41" t="s">
-        <v>383</v>
-      </c>
-      <c r="J41" t="s">
+        <v>382</v>
+      </c>
+      <c r="J41">
+        <v>6</v>
+      </c>
+      <c r="K41" t="s">
         <v>36</v>
       </c>
-      <c r="K41" t="s">
-        <v>37</v>
-      </c>
       <c r="L41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N41">
         <v>6050</v>
@@ -4487,33 +4484,33 @@
         <v>0</v>
       </c>
       <c r="R41" t="s">
+        <v>40</v>
+      </c>
+      <c r="W41" t="s">
         <v>41</v>
       </c>
-      <c r="W41" t="s">
-        <v>42</v>
-      </c>
       <c r="X41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA41" t="s">
+        <v>383</v>
+      </c>
+      <c r="AB41" t="s">
         <v>384</v>
       </c>
-      <c r="AB41" t="s">
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A42" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="42" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>386</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>387</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>388</v>
-      </c>
-      <c r="D42" t="s">
-        <v>389</v>
       </c>
       <c r="E42" t="s">
         <v>32</v>
@@ -4522,22 +4519,22 @@
         <v>33</v>
       </c>
       <c r="G42" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H42">
         <v>6</v>
       </c>
       <c r="I42" t="s">
-        <v>383</v>
-      </c>
-      <c r="J42" t="s">
+        <v>382</v>
+      </c>
+      <c r="J42">
+        <v>6</v>
+      </c>
+      <c r="K42" t="s">
         <v>36</v>
       </c>
-      <c r="K42" t="s">
-        <v>37</v>
-      </c>
       <c r="L42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N42">
         <v>6050</v>
@@ -4549,36 +4546,36 @@
         <v>0</v>
       </c>
       <c r="R42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA42" t="s">
+        <v>390</v>
+      </c>
+      <c r="AB42" t="s">
         <v>391</v>
       </c>
-      <c r="AB42" t="s">
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A43" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="43" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
         <v>393</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>394</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>395</v>
-      </c>
-      <c r="D43" t="s">
-        <v>396</v>
       </c>
       <c r="E43" t="s">
         <v>32</v>
@@ -4587,22 +4584,22 @@
         <v>33</v>
       </c>
       <c r="G43" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H43">
         <v>6</v>
       </c>
       <c r="I43" t="s">
-        <v>383</v>
-      </c>
-      <c r="J43" t="s">
+        <v>382</v>
+      </c>
+      <c r="J43">
+        <v>6</v>
+      </c>
+      <c r="K43" t="s">
         <v>36</v>
       </c>
-      <c r="K43" t="s">
-        <v>37</v>
-      </c>
       <c r="L43" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N43">
         <v>6050</v>
@@ -4614,33 +4611,33 @@
         <v>0</v>
       </c>
       <c r="R43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA43" t="s">
+        <v>397</v>
+      </c>
+      <c r="AB43" t="s">
         <v>398</v>
       </c>
-      <c r="AB43" t="s">
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A44" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="44" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>400</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>401</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>402</v>
-      </c>
-      <c r="D44" t="s">
-        <v>403</v>
       </c>
       <c r="E44" t="s">
         <v>32</v>
@@ -4649,22 +4646,22 @@
         <v>33</v>
       </c>
       <c r="G44" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H44">
         <v>6</v>
       </c>
       <c r="I44" t="s">
-        <v>383</v>
-      </c>
-      <c r="J44" t="s">
+        <v>382</v>
+      </c>
+      <c r="J44">
+        <v>6</v>
+      </c>
+      <c r="K44" t="s">
         <v>36</v>
       </c>
-      <c r="K44" t="s">
-        <v>37</v>
-      </c>
       <c r="L44" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N44">
         <v>6050</v>
@@ -4676,33 +4673,33 @@
         <v>0</v>
       </c>
       <c r="R44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA44" t="s">
+        <v>404</v>
+      </c>
+      <c r="AB44" t="s">
         <v>405</v>
       </c>
-      <c r="AB44" t="s">
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A45" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="45" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>407</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>408</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>409</v>
-      </c>
-      <c r="D45" t="s">
-        <v>410</v>
       </c>
       <c r="E45" t="s">
         <v>32</v>
@@ -4711,22 +4708,22 @@
         <v>33</v>
       </c>
       <c r="G45" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H45">
         <v>7</v>
       </c>
       <c r="I45" t="s">
-        <v>383</v>
-      </c>
-      <c r="J45" t="s">
+        <v>382</v>
+      </c>
+      <c r="J45">
+        <v>6</v>
+      </c>
+      <c r="K45" t="s">
         <v>36</v>
       </c>
-      <c r="K45" t="s">
-        <v>37</v>
-      </c>
       <c r="L45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N45">
         <v>6050</v>
@@ -4738,33 +4735,33 @@
         <v>0</v>
       </c>
       <c r="R45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA45" t="s">
+        <v>411</v>
+      </c>
+      <c r="AB45" t="s">
         <v>412</v>
       </c>
-      <c r="AB45" t="s">
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A46" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="46" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>414</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>415</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>416</v>
-      </c>
-      <c r="D46" t="s">
-        <v>417</v>
       </c>
       <c r="E46" t="s">
         <v>32</v>
@@ -4773,22 +4770,22 @@
         <v>33</v>
       </c>
       <c r="G46" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H46">
         <v>7</v>
       </c>
       <c r="I46" t="s">
-        <v>383</v>
-      </c>
-      <c r="J46" t="s">
+        <v>382</v>
+      </c>
+      <c r="J46">
+        <v>6</v>
+      </c>
+      <c r="K46" t="s">
         <v>36</v>
       </c>
-      <c r="K46" t="s">
-        <v>37</v>
-      </c>
       <c r="L46" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N46">
         <v>6050</v>
@@ -4800,33 +4797,33 @@
         <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA46" t="s">
+        <v>418</v>
+      </c>
+      <c r="AB46" t="s">
         <v>419</v>
       </c>
-      <c r="AB46" t="s">
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A47" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="47" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>421</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>422</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>423</v>
-      </c>
-      <c r="D47" t="s">
-        <v>424</v>
       </c>
       <c r="E47" t="s">
         <v>32</v>
@@ -4835,22 +4832,22 @@
         <v>33</v>
       </c>
       <c r="G47" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H47">
         <v>5</v>
       </c>
       <c r="I47" t="s">
-        <v>383</v>
-      </c>
-      <c r="J47" t="s">
+        <v>382</v>
+      </c>
+      <c r="J47">
+        <v>6</v>
+      </c>
+      <c r="K47" t="s">
         <v>36</v>
       </c>
-      <c r="K47" t="s">
-        <v>37</v>
-      </c>
       <c r="L47" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N47">
         <v>6050</v>
@@ -4862,33 +4859,33 @@
         <v>0</v>
       </c>
       <c r="R47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA47" t="s">
+        <v>425</v>
+      </c>
+      <c r="AB47" t="s">
         <v>426</v>
       </c>
-      <c r="AB47" t="s">
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.5">
+      <c r="A48" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="48" spans="1:28" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>428</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>429</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>430</v>
-      </c>
-      <c r="D48" t="s">
-        <v>431</v>
       </c>
       <c r="E48" t="s">
         <v>32</v>
@@ -4897,22 +4894,22 @@
         <v>33</v>
       </c>
       <c r="G48" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H48">
         <v>5</v>
       </c>
       <c r="I48" t="s">
-        <v>383</v>
-      </c>
-      <c r="J48" t="s">
+        <v>382</v>
+      </c>
+      <c r="J48">
+        <v>6</v>
+      </c>
+      <c r="K48" t="s">
         <v>36</v>
       </c>
-      <c r="K48" t="s">
-        <v>37</v>
-      </c>
       <c r="L48" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N48">
         <v>6050</v>
@@ -4924,26 +4921,26 @@
         <v>0</v>
       </c>
       <c r="R48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA48" t="s">
+        <v>432</v>
+      </c>
+      <c r="AB48" t="s">
         <v>433</v>
-      </c>
-      <c r="AB48" t="s">
-        <v>434</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AB1 A48:G48 K3:AB48 A2:G2 I2:AB2 A3:G13 I3:I13 A14:G14 I14 A15:G23 I15:I23 A24:G24 I24 A25:G33 I25:I33 A34:G34 I34 A35:G46 I35:I46 A47:G47 I47 I48" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AB1 A48:G48 K3:AB48 A2:G2 I2 A3:G13 I3:I13 A14:G14 I14 A15:G23 I15:I23 A24:G24 I24 A25:G33 I25:I33 A34:G34 I34 A35:G46 I35:I46 A47:G47 I47 I48 K2:AB2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>